--- a/data/processed/instances/graphs/voll_table.xlsx
+++ b/data/processed/instances/graphs/voll_table.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FarhadBillimoria\OneDrive - Aurora Energy Research\Documents\Personal\Endog_demand_AI\pyai\data\processed\instances\graphs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://auroraer-my.sharepoint.com/personal/farhad_billimoria_auroraer_com/Documents/Documents/Personal/Endog_demand_AI/pyai/data/processed/instances/graphs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CAB09122-BA78-4B64-9D93-7876A1E75D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:9_{CAB09122-BA78-4B64-9D93-7876A1E75D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB1F3F9A-CEED-4547-A828-09E2260F19F4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EE0F3C9F-908A-40EA-9D05-B964B7DDA71B}"/>
   </bookViews>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">voll_box_panel_by_gpu_ondemand_!$A$1:$G$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="113">
   <si>
     <t>gpu_model_clean</t>
   </si>
@@ -851,10 +864,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1310,10 +1323,10 @@
       <c r="G3">
         <v>3502.7864855450998</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="L3" s="2"/>
+      <c r="L3" s="3"/>
       <c r="O3" t="s">
         <v>104</v>
       </c>
@@ -1401,6 +1414,9 @@
         <f>"$"&amp;S5&amp;" - "&amp;T5&amp;"/MWh"</f>
         <v>$500 - 1700/MWh</v>
       </c>
+      <c r="N5" t="s">
+        <v>11</v>
+      </c>
       <c r="O5">
         <f>ROUND(MEDIAN($D$5:$E$18),-2)</f>
         <v>2600</v>
@@ -1453,6 +1469,9 @@
         <f t="shared" ref="L6:L8" si="1">"$"&amp;S6&amp;" - "&amp;T6&amp;"/MWh"</f>
         <v>$1100 - 3100/MWh</v>
       </c>
+      <c r="N6" t="s">
+        <v>26</v>
+      </c>
       <c r="O6">
         <f>ROUND(MEDIAN($D$67:$E$77),-2)</f>
         <v>8100</v>
@@ -1505,6 +1524,9 @@
         <f t="shared" si="1"/>
         <v>$1800 - 5700/MWh</v>
       </c>
+      <c r="N7" t="s">
+        <v>8</v>
+      </c>
       <c r="O7">
         <f>ROUND(MEDIAN($D$19:$E$66),-2)</f>
         <v>8300</v>
@@ -1556,6 +1578,9 @@
       <c r="L8" s="1" t="str">
         <f t="shared" si="1"/>
         <v>$2400 - 3300/MWh</v>
+      </c>
+      <c r="N8" t="s">
+        <v>98</v>
       </c>
       <c r="O8">
         <f>ROUND(MEDIAN($D$2:$E$4),-2)</f>

--- a/data/processed/instances/graphs/voll_table.xlsx
+++ b/data/processed/instances/graphs/voll_table.xlsx
@@ -5,18 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://auroraer-my.sharepoint.com/personal/farhad_billimoria_auroraer_com/Documents/Documents/Personal/Endog_demand_AI/pyai/data/processed/instances/graphs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FarhadBillimoria\OneDrive - Aurora Energy Research\Documents\Personal\Endog_demand_AI\pyai\data\processed\instances\graphs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:9_{CAB09122-BA78-4B64-9D93-7876A1E75D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB1F3F9A-CEED-4547-A828-09E2260F19F4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D830C9-6F59-4DA8-B47A-6320029FC84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EE0F3C9F-908A-40EA-9D05-B964B7DDA71B}"/>
   </bookViews>
   <sheets>
     <sheet name="voll_box_panel_by_gpu_ondemand_" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">voll_box_panel_by_gpu_ondemand_!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">voll_box_panel_by_gpu_ondemand_!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="117">
   <si>
     <t>gpu_model_clean</t>
   </si>
@@ -375,6 +377,18 @@
   </si>
   <si>
     <t>* The table shows the range of calculated values from the 10th percentile to the 90th percentage of computing instances analysed.</t>
+  </si>
+  <si>
+    <t>ondemand_sla_h3p0_trng_median</t>
+  </si>
+  <si>
+    <t>ondemand_sla_h3p0_inf_median</t>
+  </si>
+  <si>
+    <t>On-demand w/ SLA liability</t>
+  </si>
+  <si>
+    <t>On-demand SLA</t>
   </si>
 </sst>
 </file>
@@ -864,10 +878,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1247,15 +1261,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{609544C3-728D-45D7-8E80-16B470978117}">
-  <dimension ref="A1:T77"/>
+  <dimension ref="A1:AA77"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.90625" customWidth="1"/>
-    <col min="12" max="12" width="21.90625" customWidth="1"/>
+    <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.90625" customWidth="1"/>
+    <col min="14" max="16" width="21.90625" customWidth="1"/>
+    <col min="21" max="21" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1277,8 +1292,14 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="H1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>97</v>
       </c>
@@ -1300,8 +1321,14 @@
       <c r="G2">
         <v>2999.6505684357599</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="H2">
+        <v>69859.883114033597</v>
+      </c>
+      <c r="I2">
+        <v>85384.3015838188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -1323,24 +1350,38 @@
       <c r="G3">
         <v>3502.7864855450998</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="H3">
+        <v>89830.173838700401</v>
+      </c>
+      <c r="I3">
+        <v>109792.434691745</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="O3" t="s">
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="1"/>
+      <c r="S3" t="s">
         <v>104</v>
       </c>
-      <c r="P3" t="s">
+      <c r="T3" t="s">
         <v>105</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="U3" t="s">
+        <v>116</v>
+      </c>
+      <c r="V3" t="s">
         <v>104</v>
       </c>
-      <c r="S3" t="s">
+      <c r="X3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="Z3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -1362,32 +1403,50 @@
       <c r="G4">
         <v>2799.6810207336498</v>
       </c>
-      <c r="K4" t="s">
+      <c r="H4">
+        <v>102831.90952587999</v>
+      </c>
+      <c r="I4">
+        <v>125683.444976076</v>
+      </c>
+      <c r="M4" t="s">
         <v>109</v>
       </c>
-      <c r="L4" t="s">
+      <c r="N4" t="s">
+        <v>115</v>
+      </c>
+      <c r="O4" t="s">
         <v>110</v>
       </c>
-      <c r="O4" t="s">
+      <c r="S4" t="s">
         <v>108</v>
       </c>
-      <c r="P4" t="s">
+      <c r="T4" t="s">
         <v>108</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="U4" t="s">
+        <v>108</v>
+      </c>
+      <c r="V4" t="s">
         <v>106</v>
       </c>
-      <c r="R4" t="s">
+      <c r="W4" t="s">
         <v>107</v>
       </c>
-      <c r="S4" t="s">
+      <c r="X4" t="s">
         <v>106</v>
       </c>
-      <c r="T4" t="s">
+      <c r="Y4" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="Z4" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1403,46 +1462,69 @@
       <c r="E5">
         <v>2324.1262179315199</v>
       </c>
-      <c r="J5" t="s">
+      <c r="H5">
+        <v>15782.929861771299</v>
+      </c>
+      <c r="I5">
+        <v>19290.2476088316</v>
+      </c>
+      <c r="L5" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="1" t="str">
-        <f>"$"&amp;Q5&amp;" - "&amp;R5&amp;"/MWh"</f>
+      <c r="M5" s="1" t="str">
+        <f>"$"&amp;V5&amp;" - "&amp;W5&amp;"/MWh"</f>
         <v>$1900 - 4500/MWh</v>
       </c>
-      <c r="L5" s="1" t="str">
-        <f>"$"&amp;S5&amp;" - "&amp;T5&amp;"/MWh"</f>
+      <c r="N5" s="1" t="str">
+        <f>"$"&amp;Z5&amp;" - "&amp;AA5&amp;"/MWh"</f>
+        <v>$15500 - 37200/MWh</v>
+      </c>
+      <c r="O5" s="1" t="str">
+        <f>"$"&amp;X5&amp;" - "&amp;Y5&amp;"/MWh"</f>
         <v>$500 - 1700/MWh</v>
       </c>
-      <c r="N5" t="s">
+      <c r="P5" s="1"/>
+      <c r="R5" t="s">
         <v>11</v>
       </c>
-      <c r="O5">
+      <c r="S5">
         <f>ROUND(MEDIAN($D$5:$E$18),-2)</f>
         <v>2600</v>
       </c>
-      <c r="P5">
+      <c r="T5">
         <f>ROUND(MEDIAN($F$5:$G$18),-2)</f>
         <v>1100</v>
       </c>
-      <c r="Q5">
+      <c r="U5">
+        <f>ROUND(MEDIAN($H$5:$I$18),-2)</f>
+        <v>21700</v>
+      </c>
+      <c r="V5">
         <f>ROUND(PERCENTILE($D$5:$E$18,0.1),-2)</f>
         <v>1900</v>
       </c>
-      <c r="R5">
+      <c r="W5">
         <f>ROUND(PERCENTILE($D$5:$E$18,0.9),-2)</f>
         <v>4500</v>
       </c>
-      <c r="S5">
+      <c r="X5">
         <f>ROUND(PERCENTILE($F$5:$G$18,0.1),-2)</f>
         <v>500</v>
       </c>
-      <c r="T5">
+      <c r="Y5">
         <f>ROUND(PERCENTILE($F$5:$G$18,0.9),-2)</f>
         <v>1700</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="Z5">
+        <f>ROUND(PERCENTILE($H$5:$I$18,0.1),-2)</f>
+        <v>15500</v>
+      </c>
+      <c r="AA5">
+        <f>ROUND(PERCENTILE($H$5:$I$18,0.9),-2)</f>
+        <v>37200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1458,46 +1540,69 @@
       <c r="E6">
         <v>2324.1262179315199</v>
       </c>
-      <c r="J6" t="s">
+      <c r="H6">
+        <v>15782.929861771299</v>
+      </c>
+      <c r="I6">
+        <v>19290.2476088316</v>
+      </c>
+      <c r="L6" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="1" t="str">
-        <f t="shared" ref="K6:K8" si="0">"$"&amp;Q6&amp;" - "&amp;R6&amp;"/MWh"</f>
+      <c r="M6" s="1" t="str">
+        <f t="shared" ref="M6:N8" si="0">"$"&amp;V6&amp;" - "&amp;W6&amp;"/MWh"</f>
         <v>$6100 - 10400/MWh</v>
       </c>
-      <c r="L6" s="1" t="str">
-        <f t="shared" ref="L6:L8" si="1">"$"&amp;S6&amp;" - "&amp;T6&amp;"/MWh"</f>
+      <c r="N6" s="1" t="str">
+        <f>"$"&amp;Z6&amp;" - "&amp;AA6&amp;"/MWh"</f>
+        <v>$50800 - 86700/MWh</v>
+      </c>
+      <c r="O6" s="1" t="str">
+        <f>"$"&amp;X6&amp;" - "&amp;Y6&amp;"/MWh"</f>
         <v>$1100 - 3100/MWh</v>
       </c>
-      <c r="N6" t="s">
+      <c r="P6" s="1"/>
+      <c r="R6" t="s">
         <v>26</v>
       </c>
-      <c r="O6">
+      <c r="S6">
         <f>ROUND(MEDIAN($D$67:$E$77),-2)</f>
         <v>8100</v>
       </c>
-      <c r="P6">
+      <c r="T6">
         <f>ROUND(MEDIAN($F$67:$G$77),-2)</f>
         <v>2500</v>
       </c>
-      <c r="Q6">
+      <c r="U6">
+        <f>ROUND(MEDIAN($H$67:$I$77),-2)</f>
+        <v>66900</v>
+      </c>
+      <c r="V6">
         <f>ROUND(PERCENTILE($D$67:$E$77,0.1),-2)</f>
         <v>6100</v>
       </c>
-      <c r="R6">
+      <c r="W6">
         <f>ROUND(PERCENTILE($D$67:$E$77,0.9),-2)</f>
         <v>10400</v>
       </c>
-      <c r="S6">
+      <c r="X6">
         <f>ROUND(PERCENTILE($F$67:$G$77,0.1),-2)</f>
         <v>1100</v>
       </c>
-      <c r="T6">
+      <c r="Y6">
         <f>ROUND(PERCENTILE($F$67:$G$77,0.9),-2)</f>
         <v>3100</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="Z6">
+        <f>ROUND(PERCENTILE($H$67:$I$77,0.1),-2)</f>
+        <v>50800</v>
+      </c>
+      <c r="AA6">
+        <f>ROUND(PERCENTILE($H$67:$I$77,0.9),-2)</f>
+        <v>86700</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1513,46 +1618,69 @@
       <c r="E7">
         <v>3159.6452328159598</v>
       </c>
-      <c r="J7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K7" s="1" t="str">
+      <c r="H7">
+        <v>21456.8635355775</v>
+      </c>
+      <c r="I7">
+        <v>26225.055432372501</v>
+      </c>
+      <c r="L7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M7" s="1" t="str">
         <f t="shared" si="0"/>
         <v>$5200 - 11900/MWh</v>
       </c>
-      <c r="L7" s="1" t="str">
-        <f t="shared" si="1"/>
+      <c r="N7" s="1" t="str">
+        <f>"$"&amp;Z7&amp;" - "&amp;AA7&amp;"/MWh"</f>
+        <v>$42800 - 98500/MWh</v>
+      </c>
+      <c r="O7" s="1" t="str">
+        <f>"$"&amp;X7&amp;" - "&amp;Y7&amp;"/MWh"</f>
         <v>$1800 - 5700/MWh</v>
       </c>
-      <c r="N7" t="s">
-        <v>8</v>
-      </c>
-      <c r="O7">
+      <c r="P7" s="1"/>
+      <c r="R7" t="s">
+        <v>8</v>
+      </c>
+      <c r="S7">
         <f>ROUND(MEDIAN($D$19:$E$66),-2)</f>
         <v>8300</v>
       </c>
-      <c r="P7">
+      <c r="T7">
         <f>ROUND(MEDIAN($F$19:$G$66),-2)</f>
         <v>3300</v>
       </c>
-      <c r="Q7">
+      <c r="U7">
+        <f>ROUND(MEDIAN($H$19:$I$66),-2)</f>
+        <v>69100</v>
+      </c>
+      <c r="V7">
         <f>ROUND(PERCENTILE($D$19:$E$66,0.1),-2)</f>
         <v>5200</v>
       </c>
-      <c r="R7">
+      <c r="W7">
         <f>ROUND(PERCENTILE($D$19:$E$66,0.9),-2)</f>
         <v>11900</v>
       </c>
-      <c r="S7">
+      <c r="X7">
         <f>ROUND(PERCENTILE($F$19:$G$66,0.1),-2)</f>
         <v>1800</v>
       </c>
-      <c r="T7">
+      <c r="Y7">
         <f>ROUND(PERCENTILE($F$19:$G$66,0.9),-2)</f>
         <v>5700</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="Z7">
+        <f>ROUND(PERCENTILE($H$19:$I$66,0.1),-2)</f>
+        <v>42800</v>
+      </c>
+      <c r="AA7">
+        <f>ROUND(PERCENTILE($H$19:$I$66,0.9),-2)</f>
+        <v>98500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1568,46 +1696,69 @@
       <c r="E8">
         <v>3159.6452328159598</v>
       </c>
-      <c r="J8" t="s">
+      <c r="H8">
+        <v>21456.8635355775</v>
+      </c>
+      <c r="I8">
+        <v>26225.055432372501</v>
+      </c>
+      <c r="L8" t="s">
         <v>98</v>
       </c>
-      <c r="K8" s="1" t="str">
+      <c r="M8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>$9400 - 14200/MWh</v>
       </c>
-      <c r="L8" s="1" t="str">
-        <f t="shared" si="1"/>
+      <c r="N8" s="1" t="str">
+        <f>"$"&amp;Z8&amp;" - "&amp;AA8&amp;"/MWh"</f>
+        <v>$77600 - 117700/MWh</v>
+      </c>
+      <c r="O8" s="1" t="str">
+        <f>"$"&amp;X8&amp;" - "&amp;Y8&amp;"/MWh"</f>
         <v>$2400 - 3300/MWh</v>
       </c>
-      <c r="N8" t="s">
+      <c r="P8" s="1"/>
+      <c r="R8" t="s">
         <v>98</v>
       </c>
-      <c r="O8">
+      <c r="S8">
         <f>ROUND(MEDIAN($D$2:$E$4),-2)</f>
         <v>11600</v>
       </c>
-      <c r="P8">
+      <c r="T8">
         <f>ROUND(MEDIAN($F$2:$G$4),-2)</f>
         <v>2800</v>
       </c>
-      <c r="Q8">
+      <c r="U8">
+        <f>ROUND(MEDIAN($H$2:$I$4),-2)</f>
+        <v>96300</v>
+      </c>
+      <c r="V8">
         <f>ROUND(PERCENTILE($D$2:$E$4,0.1),-2)</f>
         <v>9400</v>
       </c>
-      <c r="R8">
+      <c r="W8">
         <f>ROUND(PERCENTILE($D$2:$E$4,0.9),-2)</f>
         <v>14200</v>
       </c>
-      <c r="S8">
+      <c r="X8">
         <f>ROUND(PERCENTILE($F$2:$G$4,0.1),-2)</f>
         <v>2400</v>
       </c>
-      <c r="T8">
+      <c r="Y8">
         <f>ROUND(PERCENTILE($F$2:$G$4,0.9),-2)</f>
         <v>3300</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="Z8">
+        <f>ROUND(PERCENTILE($H$2:$I$4,0.1),-2)</f>
+        <v>77600</v>
+      </c>
+      <c r="AA8">
+        <f>ROUND(PERCENTILE($H$2:$I$4,0.9),-2)</f>
+        <v>117700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1623,13 +1774,21 @@
       <c r="E9">
         <v>3159.6452328159598</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="H9">
+        <v>21456.8635355775</v>
+      </c>
+      <c r="I9">
+        <v>26225.055432372501</v>
+      </c>
+      <c r="L9" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1645,11 +1804,19 @@
       <c r="E10">
         <v>2396.5489694839398</v>
       </c>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
+      <c r="H10">
+        <v>16274.7461836773</v>
+      </c>
+      <c r="I10">
+        <v>19891.356446716702</v>
+      </c>
       <c r="L10" s="4"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1671,16 +1838,22 @@
       <c r="G11">
         <v>2077.6166573712499</v>
       </c>
-      <c r="O11">
+      <c r="H11">
+        <v>21891.497236728599</v>
+      </c>
+      <c r="I11">
+        <v>26756.274400446098</v>
+      </c>
+      <c r="S11">
         <f>14*1.1</f>
         <v>15.400000000000002</v>
       </c>
-      <c r="P11">
+      <c r="T11">
         <f>15*1.1</f>
         <v>16.5</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1702,8 +1875,14 @@
       <c r="G12">
         <v>1125.48301810046</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="H12">
+        <v>14949.1153142159</v>
+      </c>
+      <c r="I12">
+        <v>18271.140939597299</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1725,8 +1904,14 @@
       <c r="G13">
         <v>1352.66778211563</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="H13">
+        <v>21891.497236728599</v>
+      </c>
+      <c r="I13">
+        <v>26756.274400446098</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1748,8 +1933,14 @@
       <c r="G14">
         <v>1261.01505856107</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="H14">
+        <v>21891.497236728599</v>
+      </c>
+      <c r="I14">
+        <v>26756.274400446098</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1771,8 +1962,14 @@
       <c r="G15">
         <v>489.11651728553102</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="H15">
+        <v>10970.375974857399</v>
+      </c>
+      <c r="I15">
+        <v>13408.2373026035</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -1788,8 +1985,14 @@
       <c r="E16">
         <v>5472.7880814837299</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H16">
+        <v>37165.206335166797</v>
+      </c>
+      <c r="I16">
+        <v>45424.141076314903</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>82</v>
       </c>
@@ -1805,8 +2008,14 @@
       <c r="E17">
         <v>5472.7880814837299</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H17">
+        <v>37165.206335166797</v>
+      </c>
+      <c r="I17">
+        <v>45424.141076314903</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>82</v>
       </c>
@@ -1822,8 +2031,14 @@
       <c r="E18">
         <v>2875.8587633807301</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H18">
+        <v>19529.6954204127</v>
+      </c>
+      <c r="I18">
+        <v>23869.62773606</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -1845,8 +2060,14 @@
       <c r="G19">
         <v>9980.1940978411494</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H19">
+        <v>77977.766974558399</v>
+      </c>
+      <c r="I19">
+        <v>95306.159635571297</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1868,8 +2089,14 @@
       <c r="G20">
         <v>3016.9260169260101</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H20">
+        <v>52577.1722135358</v>
+      </c>
+      <c r="I20">
+        <v>64260.988260988197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -1891,8 +2118,14 @@
       <c r="G21">
         <v>4306.0306030602997</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H21">
+        <v>83455.036412732094</v>
+      </c>
+      <c r="I21">
+        <v>102000.600060005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -1914,8 +2147,14 @@
       <c r="G22">
         <v>5331.9559228650096</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H22">
+        <v>63481.5927873779</v>
+      </c>
+      <c r="I22">
+        <v>77588.613406795193</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -1937,8 +2176,14 @@
       <c r="G23">
         <v>2791.9580419580402</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H23">
+        <v>47963.763509217999</v>
+      </c>
+      <c r="I23">
+        <v>58622.3776223776</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -1960,8 +2205,14 @@
       <c r="G24">
         <v>4741.9077134986201</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H24">
+        <v>63481.5927873779</v>
+      </c>
+      <c r="I24">
+        <v>77588.613406795193</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -1983,8 +2234,14 @@
       <c r="G25">
         <v>3758.6029789419599</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H25">
+        <v>56643.227342765102</v>
+      </c>
+      <c r="I25">
+        <v>69230.611196712794</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -2006,8 +2263,14 @@
       <c r="G26">
         <v>5007.0568700705599</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H26">
+        <v>69008.490886448504</v>
+      </c>
+      <c r="I26">
+        <v>84343.711083437098</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -2029,8 +2292,14 @@
       <c r="G27">
         <v>3027.8038113089601</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H27">
+        <v>42684.502002215202</v>
+      </c>
+      <c r="I27">
+        <v>52169.946891596301</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>43</v>
       </c>
@@ -2052,8 +2321,14 @@
       <c r="G28">
         <v>2076.6283524904202</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H28">
+        <v>64905.101168424</v>
+      </c>
+      <c r="I28">
+        <v>79328.456983629396</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -2075,8 +2350,14 @@
       <c r="G29">
         <v>2681.4625124484201</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H29">
+        <v>42973.3441974159</v>
+      </c>
+      <c r="I29">
+        <v>52522.976241286102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -2098,8 +2379,14 @@
       <c r="G30">
         <v>2257.9281183932299</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H30">
+        <v>52834.134153373001</v>
+      </c>
+      <c r="I30">
+        <v>64575.052854122601</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>43</v>
       </c>
@@ -2121,8 +2408,14 @@
       <c r="G31">
         <v>3898.9898989898902</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H31">
+        <v>64905.101168424</v>
+      </c>
+      <c r="I31">
+        <v>79328.456983629396</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>43</v>
       </c>
@@ -2144,8 +2437,14 @@
       <c r="G32">
         <v>2287.35632183908</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H32">
+        <v>64905.101168424</v>
+      </c>
+      <c r="I32">
+        <v>79328.456983629396</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>43</v>
       </c>
@@ -2167,8 +2466,14 @@
       <c r="G33">
         <v>1589.43768392587</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H33">
+        <v>36295.958872909403</v>
+      </c>
+      <c r="I33">
+        <v>44361.727511333796</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -2190,8 +2495,14 @@
       <c r="G34">
         <v>5278.0137826866703</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H34">
+        <v>73749.285548775704</v>
+      </c>
+      <c r="I34">
+        <v>90138.015670725901</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -2213,8 +2524,14 @@
       <c r="G35">
         <v>4891.44017494532</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H35">
+        <v>90078.725398313007</v>
+      </c>
+      <c r="I35">
+        <v>110096.219931271</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -2236,8 +2553,14 @@
       <c r="G36">
         <v>6138.4976525821503</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H36">
+        <v>80613.665463857498</v>
+      </c>
+      <c r="I36">
+        <v>98527.813344714697</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -2259,8 +2582,14 @@
       <c r="G37">
         <v>5988.5568976477998</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H37">
+        <v>70341.096919609306</v>
+      </c>
+      <c r="I37">
+        <v>85972.451790633597</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>50</v>
       </c>
@@ -2282,8 +2611,14 @@
       <c r="G38">
         <v>5992.4064589557502</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H38">
+        <v>80613.665463857498</v>
+      </c>
+      <c r="I38">
+        <v>98527.813344714697</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>50</v>
       </c>
@@ -2305,8 +2640,14 @@
       <c r="G39">
         <v>5695.4375212802097</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H39">
+        <v>76487.324728387001</v>
+      </c>
+      <c r="I39">
+        <v>93484.508001361901</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>50</v>
       </c>
@@ -2328,8 +2669,14 @@
       <c r="G40">
         <v>7048.5092864125099</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H40">
+        <v>83575.313249800005</v>
+      </c>
+      <c r="I40">
+        <v>102147.605083088</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -2351,8 +2698,14 @@
       <c r="G41">
         <v>4636.0014487504504</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H41">
+        <v>65982.417437687196</v>
+      </c>
+      <c r="I41">
+        <v>80645.176868284398</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>59</v>
       </c>
@@ -2374,8 +2727,14 @@
       <c r="G42">
         <v>3017.9719270628302</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H42">
+        <v>46736.385102500797</v>
+      </c>
+      <c r="I42">
+        <v>57122.248458611997</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>59</v>
       </c>
@@ -2397,8 +2756,14 @@
       <c r="G43">
         <v>3525.5034820252199</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H43">
+        <v>96849.381448590895</v>
+      </c>
+      <c r="I43">
+        <v>118371.466214944</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>59</v>
       </c>
@@ -2420,8 +2785,14 @@
       <c r="G44">
         <v>2448.4126984126901</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H44">
+        <v>61513.419913419901</v>
+      </c>
+      <c r="I44">
+        <v>75183.068783068695</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>59</v>
       </c>
@@ -2443,8 +2814,14 @@
       <c r="G45">
         <v>2675.8658008657999</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H45">
+        <v>41195.609504132197</v>
+      </c>
+      <c r="I45">
+        <v>50350.189393939298</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>59</v>
       </c>
@@ -2466,8 +2843,14 @@
       <c r="G46">
         <v>2857.5036075036001</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H46">
+        <v>61513.419913419901</v>
+      </c>
+      <c r="I46">
+        <v>75183.068783068695</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>59</v>
       </c>
@@ -2489,8 +2872,14 @@
       <c r="G47">
         <v>3183.8553603259402</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H47">
+        <v>51951.232724494701</v>
+      </c>
+      <c r="I47">
+        <v>63495.951107715802</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>59</v>
       </c>
@@ -2512,8 +2901,14 @@
       <c r="G48">
         <v>3244.0191387559798</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H48">
+        <v>70069.061082458196</v>
+      </c>
+      <c r="I48">
+        <v>85639.963545226696</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>59</v>
       </c>
@@ -2535,8 +2930,14 @@
       <c r="G49">
         <v>2481.7762882278998</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H49">
+        <v>35296.4161937768</v>
+      </c>
+      <c r="I49">
+        <v>43140.0642368384</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -2558,8 +2959,14 @@
       <c r="G50">
         <v>5029.3255131964797</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H50">
+        <v>78828.9789389496</v>
+      </c>
+      <c r="I50">
+        <v>96346.529814271693</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -2581,8 +2988,14 @@
       <c r="G51">
         <v>5467.9863147605001</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H51">
+        <v>78828.9789389496</v>
+      </c>
+      <c r="I51">
+        <v>96346.529814271693</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -2604,8 +3017,14 @@
       <c r="G52">
         <v>3847.4633980251901</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H52">
+        <v>93412.573126566902</v>
+      </c>
+      <c r="I52">
+        <v>114170.92271024801</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>50</v>
       </c>
@@ -2627,8 +3046,14 @@
       <c r="G53">
         <v>4623.6559139784904</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H53">
+        <v>78828.9789389496</v>
+      </c>
+      <c r="I53">
+        <v>96346.529814271693</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>72</v>
       </c>
@@ -2650,8 +3075,14 @@
       <c r="G54">
         <v>2014.47199265381</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H54">
+        <v>41337.117956423703</v>
+      </c>
+      <c r="I54">
+        <v>50523.144168962303</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>72</v>
       </c>
@@ -2673,8 +3104,14 @@
       <c r="G55">
         <v>1919.59595959595</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H55">
+        <v>41337.117956423703</v>
+      </c>
+      <c r="I55">
+        <v>50523.144168962303</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>72</v>
       </c>
@@ -2696,8 +3133,14 @@
       <c r="G56">
         <v>1660.20469596628</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H56">
+        <v>36666.2755185813</v>
+      </c>
+      <c r="I56">
+        <v>44814.336744932698</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>72</v>
       </c>
@@ -2719,8 +3162,14 @@
       <c r="G57">
         <v>2155.9595959595899</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H57">
+        <v>41336.993238166702</v>
+      </c>
+      <c r="I57">
+        <v>50522.9917355371</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>72</v>
       </c>
@@ -2742,8 +3191,14 @@
       <c r="G58">
         <v>1819.4092827004199</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H58">
+        <v>41659.244690867199</v>
+      </c>
+      <c r="I58">
+        <v>50916.854622170998</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>72</v>
       </c>
@@ -2765,8 +3220,14 @@
       <c r="G59">
         <v>2071.3178294573599</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H59">
+        <v>50424.055352681098</v>
+      </c>
+      <c r="I59">
+        <v>61629.400986610199</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>50</v>
       </c>
@@ -2788,8 +3249,14 @@
       <c r="G60">
         <v>5955.0561797752798</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H60">
+        <v>88973.163710650901</v>
+      </c>
+      <c r="I60">
+        <v>108744.977868573</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>50</v>
       </c>
@@ -2811,8 +3278,14 @@
       <c r="G61">
         <v>8101.7839687194501</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H61">
+        <v>101498.53372434</v>
+      </c>
+      <c r="I61">
+        <v>124053.76344086</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>50</v>
       </c>
@@ -2834,8 +3307,14 @@
       <c r="G62">
         <v>5347.0185728250199</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H62">
+        <v>88454.412156758102</v>
+      </c>
+      <c r="I62">
+        <v>108110.94819159299</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -2857,8 +3336,14 @@
       <c r="G63">
         <v>2926.4657444005202</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H63">
+        <v>40928.8717211642</v>
+      </c>
+      <c r="I63">
+        <v>50024.176548089497</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>91</v>
       </c>
@@ -2880,8 +3365,14 @@
       <c r="G64">
         <v>4117.6712779973604</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H64">
+        <v>51161.276051023997</v>
+      </c>
+      <c r="I64">
+        <v>62530.448506807203</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>94</v>
       </c>
@@ -2903,8 +3394,14 @@
       <c r="G65">
         <v>4872.8682933228301</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H65">
+        <v>61290.114843833799</v>
+      </c>
+      <c r="I65">
+        <v>74910.140364685794</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>94</v>
       </c>
@@ -2926,8 +3423,14 @@
       <c r="G66">
         <v>5187.77056277056</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H66">
+        <v>63205.430932703603</v>
+      </c>
+      <c r="I66">
+        <v>77251.082251082204</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>25</v>
       </c>
@@ -2949,8 +3452,14 @@
       <c r="G67">
         <v>2651.4120799835</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H67">
+        <v>54764.041153651502</v>
+      </c>
+      <c r="I67">
+        <v>66933.828076685197</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -2972,8 +3481,14 @@
       <c r="G68">
         <v>3473.5930735930701</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H68">
+        <v>85293.034238488704</v>
+      </c>
+      <c r="I68">
+        <v>104247.04184704099</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>25</v>
       </c>
@@ -2995,8 +3510,14 @@
       <c r="G69">
         <v>2758.0567580567499</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H69">
+        <v>49127.115308933397</v>
+      </c>
+      <c r="I69">
+        <v>60044.252044252004</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>25</v>
       </c>
@@ -3018,8 +3539,14 @@
       <c r="G70">
         <v>3096.6810966810899</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H70">
+        <v>58991.735537189998</v>
+      </c>
+      <c r="I70">
+        <v>72101.010101010004</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>25</v>
       </c>
@@ -3041,8 +3568,14 @@
       <c r="G71">
         <v>3133.2371332371299</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H71">
+        <v>71077.528532073906</v>
+      </c>
+      <c r="I71">
+        <v>86872.534872534801</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>25</v>
       </c>
@@ -3064,8 +3597,14 @@
       <c r="G72">
         <v>3215.5225726654198</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H72">
+        <v>54764.041153651502</v>
+      </c>
+      <c r="I72">
+        <v>66933.828076685197</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>25</v>
       </c>
@@ -3087,8 +3626,14 @@
       <c r="G73">
         <v>2535.0649350649301</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H73">
+        <v>41235.419126328197</v>
+      </c>
+      <c r="I73">
+        <v>50398.845598845597</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>86</v>
       </c>
@@ -3110,8 +3655,14 @@
       <c r="G74">
         <v>1659.8890240194501</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H74">
+        <v>63180.850769783501</v>
+      </c>
+      <c r="I74">
+        <v>77221.039829735499</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>86</v>
       </c>
@@ -3133,8 +3684,14 @@
       <c r="G75">
         <v>1035.5731225296399</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H75">
+        <v>63180.850769783501</v>
+      </c>
+      <c r="I75">
+        <v>77221.039829735499</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>86</v>
       </c>
@@ -3156,8 +3713,14 @@
       <c r="G76">
         <v>1332.54788689571</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H76">
+        <v>63180.850769783501</v>
+      </c>
+      <c r="I76">
+        <v>77221.039829735499</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -3179,17 +3742,1346 @@
       <c r="G77">
         <v>2588.0681818181802</v>
       </c>
+      <c r="H77">
+        <v>74339.876033057793</v>
+      </c>
+      <c r="I77">
+        <v>90859.848484848393</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{609544C3-728D-45D7-8E80-16B470978117}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G77">
+  <autoFilter ref="A1:I1" xr:uid="{609544C3-728D-45D7-8E80-16B470978117}"/>
+  <mergeCells count="2">
+    <mergeCell ref="L9:N10"/>
+    <mergeCell ref="M3:O3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="N5:N8" formula="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53B82B0B-DBB3-4D30-BC4C-DDE53B559AE4}">
+  <dimension ref="A1:E77"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2">
+        <v>69859.883114033597</v>
+      </c>
+      <c r="E2">
+        <v>85384.3015838188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3">
+        <v>89830.173838700401</v>
+      </c>
+      <c r="E3">
+        <v>109792.434691745</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4">
+        <v>102831.90952587999</v>
+      </c>
+      <c r="E4">
+        <v>125683.444976076</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>15782.929861771299</v>
+      </c>
+      <c r="E5">
+        <v>19290.2476088316</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>15782.929861771299</v>
+      </c>
+      <c r="E6">
+        <v>19290.2476088316</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>21456.8635355775</v>
+      </c>
+      <c r="E7">
+        <v>26225.055432372501</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8">
+        <v>21456.8635355775</v>
+      </c>
+      <c r="E8">
+        <v>26225.055432372501</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9">
+        <v>21456.8635355775</v>
+      </c>
+      <c r="E9">
+        <v>26225.055432372501</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10">
+        <v>16274.7461836773</v>
+      </c>
+      <c r="E10">
+        <v>19891.356446716702</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>21891.497236728599</v>
+      </c>
+      <c r="E11">
+        <v>26756.274400446098</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12">
+        <v>14949.1153142159</v>
+      </c>
+      <c r="E12">
+        <v>18271.140939597299</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13">
+        <v>21891.497236728599</v>
+      </c>
+      <c r="E13">
+        <v>26756.274400446098</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14">
+        <v>21891.497236728599</v>
+      </c>
+      <c r="E14">
+        <v>26756.274400446098</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15">
+        <v>10970.375974857399</v>
+      </c>
+      <c r="E15">
+        <v>13408.2373026035</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16">
+        <v>37165.206335166797</v>
+      </c>
+      <c r="E16">
+        <v>45424.141076314903</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17">
+        <v>37165.206335166797</v>
+      </c>
+      <c r="E17">
+        <v>45424.141076314903</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18">
+        <v>19529.6954204127</v>
+      </c>
+      <c r="E18">
+        <v>23869.62773606</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19">
+        <v>77977.766974558399</v>
+      </c>
+      <c r="E19">
+        <v>95306.159635571297</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20">
+        <v>52577.1722135358</v>
+      </c>
+      <c r="E20">
+        <v>64260.988260988197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21">
+        <v>83455.036412732094</v>
+      </c>
+      <c r="E21">
+        <v>102000.600060005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22">
+        <v>63481.5927873779</v>
+      </c>
+      <c r="E22">
+        <v>77588.613406795193</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23">
+        <v>47963.763509217999</v>
+      </c>
+      <c r="E23">
+        <v>58622.3776223776</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24">
+        <v>63481.5927873779</v>
+      </c>
+      <c r="E24">
+        <v>77588.613406795193</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25">
+        <v>56643.227342765102</v>
+      </c>
+      <c r="E25">
+        <v>69230.611196712794</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26">
+        <v>69008.490886448504</v>
+      </c>
+      <c r="E26">
+        <v>84343.711083437098</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27">
+        <v>42684.502002215202</v>
+      </c>
+      <c r="E27">
+        <v>52169.946891596301</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28">
+        <v>64905.101168424</v>
+      </c>
+      <c r="E28">
+        <v>79328.456983629396</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29">
+        <v>42973.3441974159</v>
+      </c>
+      <c r="E29">
+        <v>52522.976241286102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30">
+        <v>52834.134153373001</v>
+      </c>
+      <c r="E30">
+        <v>64575.052854122601</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31">
+        <v>64905.101168424</v>
+      </c>
+      <c r="E31">
+        <v>79328.456983629396</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32">
+        <v>64905.101168424</v>
+      </c>
+      <c r="E32">
+        <v>79328.456983629396</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33">
+        <v>36295.958872909403</v>
+      </c>
+      <c r="E33">
+        <v>44361.727511333796</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34">
+        <v>73749.285548775704</v>
+      </c>
+      <c r="E34">
+        <v>90138.015670725901</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35">
+        <v>90078.725398313007</v>
+      </c>
+      <c r="E35">
+        <v>110096.219931271</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36">
+        <v>80613.665463857498</v>
+      </c>
+      <c r="E36">
+        <v>98527.813344714697</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37">
+        <v>70341.096919609306</v>
+      </c>
+      <c r="E37">
+        <v>85972.451790633597</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38">
+        <v>80613.665463857498</v>
+      </c>
+      <c r="E38">
+        <v>98527.813344714697</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39">
+        <v>76487.324728387001</v>
+      </c>
+      <c r="E39">
+        <v>93484.508001361901</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40">
+        <v>83575.313249800005</v>
+      </c>
+      <c r="E40">
+        <v>102147.605083088</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41">
+        <v>65982.417437687196</v>
+      </c>
+      <c r="E41">
+        <v>80645.176868284398</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42">
+        <v>46736.385102500797</v>
+      </c>
+      <c r="E42">
+        <v>57122.248458611997</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" t="s">
+        <v>61</v>
+      </c>
+      <c r="D43">
+        <v>96849.381448590895</v>
+      </c>
+      <c r="E43">
+        <v>118371.466214944</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" t="s">
+        <v>62</v>
+      </c>
+      <c r="D44">
+        <v>61513.419913419901</v>
+      </c>
+      <c r="E44">
+        <v>75183.068783068695</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>59</v>
+      </c>
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>63</v>
+      </c>
+      <c r="D45">
+        <v>41195.609504132197</v>
+      </c>
+      <c r="E45">
+        <v>50350.189393939298</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" t="s">
+        <v>64</v>
+      </c>
+      <c r="D46">
+        <v>61513.419913419901</v>
+      </c>
+      <c r="E46">
+        <v>75183.068783068695</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" t="s">
+        <v>65</v>
+      </c>
+      <c r="D47">
+        <v>51951.232724494701</v>
+      </c>
+      <c r="E47">
+        <v>63495.951107715802</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" t="s">
+        <v>66</v>
+      </c>
+      <c r="D48">
+        <v>70069.061082458196</v>
+      </c>
+      <c r="E48">
+        <v>85639.963545226696</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D49">
+        <v>35296.4161937768</v>
+      </c>
+      <c r="E49">
+        <v>43140.0642368384</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50">
+        <v>78828.9789389496</v>
+      </c>
+      <c r="E50">
+        <v>96346.529814271693</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51">
+        <v>78828.9789389496</v>
+      </c>
+      <c r="E51">
+        <v>96346.529814271693</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" t="s">
+        <v>70</v>
+      </c>
+      <c r="D52">
+        <v>93412.573126566902</v>
+      </c>
+      <c r="E52">
+        <v>114170.92271024801</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>50</v>
+      </c>
+      <c r="B53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" t="s">
+        <v>71</v>
+      </c>
+      <c r="D53">
+        <v>78828.9789389496</v>
+      </c>
+      <c r="E53">
+        <v>96346.529814271693</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>72</v>
+      </c>
+      <c r="B54" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" t="s">
+        <v>73</v>
+      </c>
+      <c r="D54">
+        <v>41337.117956423703</v>
+      </c>
+      <c r="E54">
+        <v>50523.144168962303</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" t="s">
+        <v>74</v>
+      </c>
+      <c r="D55">
+        <v>41337.117956423703</v>
+      </c>
+      <c r="E55">
+        <v>50523.144168962303</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>72</v>
+      </c>
+      <c r="B56" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" t="s">
+        <v>75</v>
+      </c>
+      <c r="D56">
+        <v>36666.2755185813</v>
+      </c>
+      <c r="E56">
+        <v>44814.336744932698</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>72</v>
+      </c>
+      <c r="B57" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" t="s">
+        <v>76</v>
+      </c>
+      <c r="D57">
+        <v>41336.993238166702</v>
+      </c>
+      <c r="E57">
+        <v>50522.9917355371</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>72</v>
+      </c>
+      <c r="B58" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" t="s">
+        <v>77</v>
+      </c>
+      <c r="D58">
+        <v>41659.244690867199</v>
+      </c>
+      <c r="E58">
+        <v>50916.854622170998</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>72</v>
+      </c>
+      <c r="B59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" t="s">
+        <v>78</v>
+      </c>
+      <c r="D59">
+        <v>50424.055352681098</v>
+      </c>
+      <c r="E59">
+        <v>61629.400986610199</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>50</v>
+      </c>
+      <c r="B60" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" t="s">
+        <v>79</v>
+      </c>
+      <c r="D60">
+        <v>88973.163710650901</v>
+      </c>
+      <c r="E60">
+        <v>108744.977868573</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>50</v>
+      </c>
+      <c r="B61" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" t="s">
+        <v>80</v>
+      </c>
+      <c r="D61">
+        <v>101498.53372434</v>
+      </c>
+      <c r="E61">
+        <v>124053.76344086</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>50</v>
+      </c>
+      <c r="B62" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" t="s">
+        <v>81</v>
+      </c>
+      <c r="D62">
+        <v>88454.412156758102</v>
+      </c>
+      <c r="E62">
+        <v>108110.94819159299</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>91</v>
+      </c>
+      <c r="B63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" t="s">
+        <v>92</v>
+      </c>
+      <c r="D63">
+        <v>40928.8717211642</v>
+      </c>
+      <c r="E63">
+        <v>50024.176548089497</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>91</v>
+      </c>
+      <c r="B64" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64" t="s">
+        <v>93</v>
+      </c>
+      <c r="D64">
+        <v>51161.276051023997</v>
+      </c>
+      <c r="E64">
+        <v>62530.448506807203</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>94</v>
+      </c>
+      <c r="B65" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" t="s">
+        <v>95</v>
+      </c>
+      <c r="D65">
+        <v>61290.114843833799</v>
+      </c>
+      <c r="E65">
+        <v>74910.140364685794</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>94</v>
+      </c>
+      <c r="B66" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66" t="s">
+        <v>96</v>
+      </c>
+      <c r="D66">
+        <v>63205.430932703603</v>
+      </c>
+      <c r="E66">
+        <v>77251.082251082204</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>25</v>
+      </c>
+      <c r="B67" t="s">
+        <v>26</v>
+      </c>
+      <c r="C67" t="s">
+        <v>27</v>
+      </c>
+      <c r="D67">
+        <v>54764.041153651502</v>
+      </c>
+      <c r="E67">
+        <v>66933.828076685197</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>25</v>
+      </c>
+      <c r="B68" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68">
+        <v>85293.034238488704</v>
+      </c>
+      <c r="E68">
+        <v>104247.04184704099</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>25</v>
+      </c>
+      <c r="B69" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" t="s">
+        <v>29</v>
+      </c>
+      <c r="D69">
+        <v>49127.115308933397</v>
+      </c>
+      <c r="E69">
+        <v>60044.252044252004</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>25</v>
+      </c>
+      <c r="B70" t="s">
+        <v>26</v>
+      </c>
+      <c r="C70" t="s">
+        <v>30</v>
+      </c>
+      <c r="D70">
+        <v>58991.735537189998</v>
+      </c>
+      <c r="E70">
+        <v>72101.010101010004</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>25</v>
+      </c>
+      <c r="B71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" t="s">
+        <v>31</v>
+      </c>
+      <c r="D71">
+        <v>71077.528532073906</v>
+      </c>
+      <c r="E71">
+        <v>86872.534872534801</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>25</v>
+      </c>
+      <c r="B72" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72" t="s">
+        <v>32</v>
+      </c>
+      <c r="D72">
+        <v>54764.041153651502</v>
+      </c>
+      <c r="E72">
+        <v>66933.828076685197</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" t="s">
+        <v>26</v>
+      </c>
+      <c r="C73" t="s">
+        <v>33</v>
+      </c>
+      <c r="D73">
+        <v>41235.419126328197</v>
+      </c>
+      <c r="E73">
+        <v>50398.845598845597</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>86</v>
+      </c>
+      <c r="B74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C74" t="s">
+        <v>87</v>
+      </c>
+      <c r="D74">
+        <v>63180.850769783501</v>
+      </c>
+      <c r="E74">
+        <v>77221.039829735499</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>86</v>
+      </c>
+      <c r="B75" t="s">
+        <v>26</v>
+      </c>
+      <c r="C75" t="s">
+        <v>88</v>
+      </c>
+      <c r="D75">
+        <v>63180.850769783501</v>
+      </c>
+      <c r="E75">
+        <v>77221.039829735499</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>86</v>
+      </c>
+      <c r="B76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" t="s">
+        <v>89</v>
+      </c>
+      <c r="D76">
+        <v>63180.850769783501</v>
+      </c>
+      <c r="E76">
+        <v>77221.039829735499</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>86</v>
+      </c>
+      <c r="B77" t="s">
+        <v>26</v>
+      </c>
+      <c r="C77" t="s">
+        <v>90</v>
+      </c>
+      <c r="D77">
+        <v>74339.876033057793</v>
+      </c>
+      <c r="E77">
+        <v>90859.848484848393</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E1" xr:uid="{53B82B0B-DBB3-4D30-BC4C-DDE53B559AE4}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E77">
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
-  <mergeCells count="2">
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="J9:L10"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/processed/instances/graphs/voll_table.xlsx
+++ b/data/processed/instances/graphs/voll_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FarhadBillimoria\OneDrive - Aurora Energy Research\Documents\Personal\Endog_demand_AI\pyai\data\processed\instances\graphs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://auroraer-my.sharepoint.com/personal/farhad_billimoria_auroraer_com/Documents/Documents/Personal/Endog_demand_AI/pyai/data/processed/instances/graphs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D830C9-6F59-4DA8-B47A-6320029FC84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{B9D830C9-6F59-4DA8-B47A-6320029FC84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77566856-12F3-41BC-B3CF-A294C2D2F690}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EE0F3C9F-908A-40EA-9D05-B964B7DDA71B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EE0F3C9F-908A-40EA-9D05-B964B7DDA71B}"/>
   </bookViews>
   <sheets>
     <sheet name="voll_box_panel_by_gpu_ondemand_" sheetId="1" r:id="rId1"/>
@@ -881,10 +881,10 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1262,15 +1262,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{609544C3-728D-45D7-8E80-16B470978117}">
   <dimension ref="A1:AA77"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.90625" customWidth="1"/>
-    <col min="14" max="16" width="21.90625" customWidth="1"/>
-    <col min="21" max="21" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.85546875" customWidth="1"/>
+    <col min="14" max="16" width="21.85546875" customWidth="1"/>
+    <col min="21" max="21" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>97</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>85384.3015838188</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:27" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -1356,11 +1356,11 @@
       <c r="I3">
         <v>109792.434691745</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
       <c r="P3" s="1"/>
       <c r="S3" t="s">
         <v>104</v>
@@ -1381,7 +1381,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1473,58 +1473,58 @@
       </c>
       <c r="M5" s="1" t="str">
         <f>"$"&amp;V5&amp;" - "&amp;W5&amp;"/MWh"</f>
-        <v>$1900 - 4500/MWh</v>
+        <v>$2200 - 4800/MWh</v>
       </c>
       <c r="N5" s="1" t="str">
         <f>"$"&amp;Z5&amp;" - "&amp;AA5&amp;"/MWh"</f>
-        <v>$15500 - 37200/MWh</v>
+        <v>$18600 - 39800/MWh</v>
       </c>
       <c r="O5" s="1" t="str">
         <f>"$"&amp;X5&amp;" - "&amp;Y5&amp;"/MWh"</f>
-        <v>$500 - 1700/MWh</v>
+        <v>$700 - 1800/MWh</v>
       </c>
       <c r="P5" s="1"/>
       <c r="R5" t="s">
         <v>11</v>
       </c>
       <c r="S5">
-        <f>ROUND(MEDIAN($D$5:$E$18),-2)</f>
-        <v>2600</v>
+        <f>ROUND(MEDIAN($E$5:$E$18),-2)</f>
+        <v>3200</v>
       </c>
       <c r="T5">
-        <f>ROUND(MEDIAN($F$5:$G$18),-2)</f>
-        <v>1100</v>
+        <f>ROUND(MEDIAN($G$5:$G$18),-2)</f>
+        <v>1300</v>
       </c>
       <c r="U5">
-        <f>ROUND(MEDIAN($H$5:$I$18),-2)</f>
-        <v>21700</v>
+        <f>ROUND(MEDIAN($I$5:$I$18),-2)</f>
+        <v>26200</v>
       </c>
       <c r="V5">
-        <f>ROUND(PERCENTILE($D$5:$E$18,0.1),-2)</f>
-        <v>1900</v>
+        <f>ROUND(PERCENTILE($E$5:$E$18,0.1),-2)</f>
+        <v>2200</v>
       </c>
       <c r="W5">
-        <f>ROUND(PERCENTILE($D$5:$E$18,0.9),-2)</f>
-        <v>4500</v>
+        <f>ROUND(PERCENTILE($E$5:$E$18,0.9),-2)</f>
+        <v>4800</v>
       </c>
       <c r="X5">
-        <f>ROUND(PERCENTILE($F$5:$G$18,0.1),-2)</f>
-        <v>500</v>
+        <f>ROUND(PERCENTILE($G$5:$G$18,0.1),-2)</f>
+        <v>700</v>
       </c>
       <c r="Y5">
-        <f>ROUND(PERCENTILE($F$5:$G$18,0.9),-2)</f>
-        <v>1700</v>
+        <f>ROUND(PERCENTILE($G$5:$G$18,0.9),-2)</f>
+        <v>1800</v>
       </c>
       <c r="Z5">
-        <f>ROUND(PERCENTILE($H$5:$I$18,0.1),-2)</f>
-        <v>15500</v>
+        <f>ROUND(PERCENTILE($I$5:$I$18,0.1),-2)</f>
+        <v>18600</v>
       </c>
       <c r="AA5">
-        <f>ROUND(PERCENTILE($H$5:$I$18,0.9),-2)</f>
-        <v>37200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
+        <f>ROUND(PERCENTILE($I$5:$I$18,0.9),-2)</f>
+        <v>39800</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1550,59 +1550,59 @@
         <v>26</v>
       </c>
       <c r="M6" s="1" t="str">
-        <f t="shared" ref="M6:N8" si="0">"$"&amp;V6&amp;" - "&amp;W6&amp;"/MWh"</f>
-        <v>$6100 - 10400/MWh</v>
+        <f t="shared" ref="M6:M8" si="0">"$"&amp;V6&amp;" - "&amp;W6&amp;"/MWh"</f>
+        <v>$7200 - 10900/MWh</v>
       </c>
       <c r="N6" s="1" t="str">
         <f>"$"&amp;Z6&amp;" - "&amp;AA6&amp;"/MWh"</f>
-        <v>$50800 - 86700/MWh</v>
+        <v>$60000 - 90900/MWh</v>
       </c>
       <c r="O6" s="1" t="str">
         <f>"$"&amp;X6&amp;" - "&amp;Y6&amp;"/MWh"</f>
-        <v>$1100 - 3100/MWh</v>
+        <v>$1300 - 3200/MWh</v>
       </c>
       <c r="P6" s="1"/>
       <c r="R6" t="s">
         <v>26</v>
       </c>
       <c r="S6">
-        <f>ROUND(MEDIAN($D$67:$E$77),-2)</f>
-        <v>8100</v>
+        <f>ROUND(MEDIAN($E$67:$E$77),-2)</f>
+        <v>9300</v>
       </c>
       <c r="T6">
-        <f>ROUND(MEDIAN($F$67:$G$77),-2)</f>
-        <v>2500</v>
+        <f>ROUND(MEDIAN($G$67:$G$77),-2)</f>
+        <v>2700</v>
       </c>
       <c r="U6">
-        <f>ROUND(MEDIAN($H$67:$I$77),-2)</f>
-        <v>66900</v>
+        <f>ROUND(MEDIAN($I$67:$I$77),-2)</f>
+        <v>77200</v>
       </c>
       <c r="V6">
-        <f>ROUND(PERCENTILE($D$67:$E$77,0.1),-2)</f>
-        <v>6100</v>
+        <f>ROUND(PERCENTILE($E$67:$E$77,0.1),-2)</f>
+        <v>7200</v>
       </c>
       <c r="W6">
-        <f>ROUND(PERCENTILE($D$67:$E$77,0.9),-2)</f>
-        <v>10400</v>
+        <f>ROUND(PERCENTILE($E$67:$E$77,0.9),-2)</f>
+        <v>10900</v>
       </c>
       <c r="X6">
-        <f>ROUND(PERCENTILE($F$67:$G$77,0.1),-2)</f>
-        <v>1100</v>
+        <f>ROUND(PERCENTILE($G$67:$G$77,0.1),-2)</f>
+        <v>1300</v>
       </c>
       <c r="Y6">
-        <f>ROUND(PERCENTILE($F$67:$G$77,0.9),-2)</f>
-        <v>3100</v>
+        <f>ROUND(PERCENTILE($G$67:$G$77,0.9),-2)</f>
+        <v>3200</v>
       </c>
       <c r="Z6">
-        <f>ROUND(PERCENTILE($H$67:$I$77,0.1),-2)</f>
-        <v>50800</v>
+        <f>ROUND(PERCENTILE($I$67:$I$77,0.1),-2)</f>
+        <v>60000</v>
       </c>
       <c r="AA6">
-        <f>ROUND(PERCENTILE($H$67:$I$77,0.9),-2)</f>
-        <v>86700</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
+        <f>ROUND(PERCENTILE($I$67:$I$77,0.9),-2)</f>
+        <v>90900</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1629,58 +1629,58 @@
       </c>
       <c r="M7" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>$5200 - 11900/MWh</v>
+        <v>$6100 - 13000/MWh</v>
       </c>
       <c r="N7" s="1" t="str">
         <f>"$"&amp;Z7&amp;" - "&amp;AA7&amp;"/MWh"</f>
-        <v>$42800 - 98500/MWh</v>
+        <v>$50500 - 108300/MWh</v>
       </c>
       <c r="O7" s="1" t="str">
         <f>"$"&amp;X7&amp;" - "&amp;Y7&amp;"/MWh"</f>
-        <v>$1800 - 5700/MWh</v>
+        <v>$2100 - 6000/MWh</v>
       </c>
       <c r="P7" s="1"/>
       <c r="R7" t="s">
         <v>8</v>
       </c>
       <c r="S7">
-        <f>ROUND(MEDIAN($D$19:$E$66),-2)</f>
-        <v>8300</v>
+        <f>ROUND(MEDIAN($E$19:$E$66),-2)</f>
+        <v>9300</v>
       </c>
       <c r="T7">
-        <f>ROUND(MEDIAN($F$19:$G$66),-2)</f>
-        <v>3300</v>
+        <f>ROUND(MEDIAN($G$19:$G$66),-2)</f>
+        <v>3800</v>
       </c>
       <c r="U7">
-        <f>ROUND(MEDIAN($H$19:$I$66),-2)</f>
-        <v>69100</v>
+        <f>ROUND(MEDIAN($I$19:$I$66),-2)</f>
+        <v>77600</v>
       </c>
       <c r="V7">
-        <f>ROUND(PERCENTILE($D$19:$E$66,0.1),-2)</f>
-        <v>5200</v>
+        <f>ROUND(PERCENTILE($E$19:$E$66,0.1),-2)</f>
+        <v>6100</v>
       </c>
       <c r="W7">
-        <f>ROUND(PERCENTILE($D$19:$E$66,0.9),-2)</f>
-        <v>11900</v>
+        <f>ROUND(PERCENTILE($E$19:$E$66,0.9),-2)</f>
+        <v>13000</v>
       </c>
       <c r="X7">
-        <f>ROUND(PERCENTILE($F$19:$G$66,0.1),-2)</f>
-        <v>1800</v>
+        <f>ROUND(PERCENTILE($G$19:$G$66,0.1),-2)</f>
+        <v>2100</v>
       </c>
       <c r="Y7">
-        <f>ROUND(PERCENTILE($F$19:$G$66,0.9),-2)</f>
-        <v>5700</v>
+        <f>ROUND(PERCENTILE($G$19:$G$66,0.9),-2)</f>
+        <v>6000</v>
       </c>
       <c r="Z7">
-        <f>ROUND(PERCENTILE($H$19:$I$66,0.1),-2)</f>
-        <v>42800</v>
+        <f>ROUND(PERCENTILE($I$19:$I$66,0.1),-2)</f>
+        <v>50500</v>
       </c>
       <c r="AA7">
-        <f>ROUND(PERCENTILE($H$19:$I$66,0.9),-2)</f>
-        <v>98500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
+        <f>ROUND(PERCENTILE($I$19:$I$66,0.9),-2)</f>
+        <v>108300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1707,58 +1707,58 @@
       </c>
       <c r="M8" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>$9400 - 14200/MWh</v>
+        <v>$10900 - 14800/MWh</v>
       </c>
       <c r="N8" s="1" t="str">
         <f>"$"&amp;Z8&amp;" - "&amp;AA8&amp;"/MWh"</f>
-        <v>$77600 - 117700/MWh</v>
+        <v>$90300 - 122500/MWh</v>
       </c>
       <c r="O8" s="1" t="str">
         <f>"$"&amp;X8&amp;" - "&amp;Y8&amp;"/MWh"</f>
-        <v>$2400 - 3300/MWh</v>
+        <v>$2800 - 3400/MWh</v>
       </c>
       <c r="P8" s="1"/>
       <c r="R8" t="s">
         <v>98</v>
       </c>
       <c r="S8">
-        <f>ROUND(MEDIAN($D$2:$E$4),-2)</f>
-        <v>11600</v>
+        <f>ROUND(MEDIAN($E$2:$E$4),-2)</f>
+        <v>13200</v>
       </c>
       <c r="T8">
-        <f>ROUND(MEDIAN($F$2:$G$4),-2)</f>
+        <f>ROUND(MEDIAN($G$2:$G$4),-2)</f>
+        <v>3000</v>
+      </c>
+      <c r="U8">
+        <f>ROUND(MEDIAN($I$2:$I$4),-2)</f>
+        <v>109800</v>
+      </c>
+      <c r="V8">
+        <f>ROUND(PERCENTILE($E$2:$E$4,0.1),-2)</f>
+        <v>10900</v>
+      </c>
+      <c r="W8">
+        <f>ROUND(PERCENTILE($E$2:$E$4,0.9),-2)</f>
+        <v>14800</v>
+      </c>
+      <c r="X8">
+        <f>ROUND(PERCENTILE($G$2:$G$4,0.1),-2)</f>
         <v>2800</v>
       </c>
-      <c r="U8">
-        <f>ROUND(MEDIAN($H$2:$I$4),-2)</f>
-        <v>96300</v>
-      </c>
-      <c r="V8">
-        <f>ROUND(PERCENTILE($D$2:$E$4,0.1),-2)</f>
-        <v>9400</v>
-      </c>
-      <c r="W8">
-        <f>ROUND(PERCENTILE($D$2:$E$4,0.9),-2)</f>
-        <v>14200</v>
-      </c>
-      <c r="X8">
-        <f>ROUND(PERCENTILE($F$2:$G$4,0.1),-2)</f>
-        <v>2400</v>
-      </c>
       <c r="Y8">
-        <f>ROUND(PERCENTILE($F$2:$G$4,0.9),-2)</f>
-        <v>3300</v>
+        <f>ROUND(PERCENTILE($G$2:$G$4,0.9),-2)</f>
+        <v>3400</v>
       </c>
       <c r="Z8">
-        <f>ROUND(PERCENTILE($H$2:$I$4,0.1),-2)</f>
-        <v>77600</v>
+        <f>ROUND(PERCENTILE($I$2:$I$4,0.1),-2)</f>
+        <v>90300</v>
       </c>
       <c r="AA8">
-        <f>ROUND(PERCENTILE($H$2:$I$4,0.9),-2)</f>
-        <v>117700</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
+        <f>ROUND(PERCENTILE($I$2:$I$4,0.9),-2)</f>
+        <v>122500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1780,15 +1780,15 @@
       <c r="I9">
         <v>26225.055432372501</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1810,13 +1810,13 @@
       <c r="I10">
         <v>19891.356446716702</v>
       </c>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>18271.140939597299</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>26756.274400446098</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>26756.274400446098</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>13408.2373026035</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>45424.141076314903</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>82</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>45424.141076314903</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>82</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>23869.62773606</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>95306.159635571297</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>64260.988260988197</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>102000.600060005</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>77588.613406795193</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>58622.3776223776</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>77588.613406795193</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>69230.611196712794</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>84343.711083437098</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>52169.946891596301</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>43</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>79328.456983629396</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>52522.976241286102</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>64575.052854122601</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>43</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>79328.456983629396</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>43</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>79328.456983629396</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>43</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>44361.727511333796</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>90138.015670725901</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>110096.219931271</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>98527.813344714697</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>85972.451790633597</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>50</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>98527.813344714697</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>50</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>93484.508001361901</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>50</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>102147.605083088</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>80645.176868284398</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>59</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>57122.248458611997</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>59</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>118371.466214944</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>59</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>75183.068783068695</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>59</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>50350.189393939298</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>59</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>75183.068783068695</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>59</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>63495.951107715802</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>59</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>85639.963545226696</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>59</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>43140.0642368384</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>96346.529814271693</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>96346.529814271693</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>114170.92271024801</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>50</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>96346.529814271693</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>72</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>50523.144168962303</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>72</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>50523.144168962303</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>72</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>44814.336744932698</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>72</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>50522.9917355371</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>72</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>50916.854622170998</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>72</v>
       </c>
@@ -3227,7 +3227,7 @@
         <v>61629.400986610199</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>50</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>108744.977868573</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>50</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>124053.76344086</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>50</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>108110.94819159299</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>50024.176548089497</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>91</v>
       </c>
@@ -3372,7 +3372,7 @@
         <v>62530.448506807203</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>94</v>
       </c>
@@ -3401,7 +3401,7 @@
         <v>74910.140364685794</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>94</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>77251.082251082204</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>25</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>66933.828076685197</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -3488,7 +3488,7 @@
         <v>104247.04184704099</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>25</v>
       </c>
@@ -3517,7 +3517,7 @@
         <v>60044.252044252004</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>25</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>72101.010101010004</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>25</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>86872.534872534801</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>25</v>
       </c>
@@ -3604,7 +3604,7 @@
         <v>66933.828076685197</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>25</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>50398.845598845597</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>86</v>
       </c>
@@ -3662,7 +3662,7 @@
         <v>77221.039829735499</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>86</v>
       </c>
@@ -3691,7 +3691,7 @@
         <v>77221.039829735499</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>86</v>
       </c>
@@ -3720,7 +3720,7 @@
         <v>77221.039829735499</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -3765,9 +3765,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53B82B0B-DBB3-4D30-BC4C-DDE53B559AE4}">
   <dimension ref="A1:E77"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>97</v>
       </c>
@@ -3801,7 +3801,7 @@
         <v>85384.3015838188</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>109792.434691745</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -3835,7 +3835,7 @@
         <v>125683.444976076</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>19290.2476088316</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>19290.2476088316</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -3886,7 +3886,7 @@
         <v>26225.055432372501</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>26225.055432372501</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -3920,7 +3920,7 @@
         <v>26225.055432372501</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>19891.356446716702</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -3954,7 +3954,7 @@
         <v>26756.274400446098</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>18271.140939597299</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -3988,7 +3988,7 @@
         <v>26756.274400446098</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -4005,7 +4005,7 @@
         <v>26756.274400446098</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>13408.2373026035</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -4039,7 +4039,7 @@
         <v>45424.141076314903</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>82</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>45424.141076314903</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>82</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>23869.62773606</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -4090,7 +4090,7 @@
         <v>95306.159635571297</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -4107,7 +4107,7 @@
         <v>64260.988260988197</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>102000.600060005</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>77588.613406795193</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>58622.3776223776</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>77588.613406795193</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>69230.611196712794</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>84343.711083437098</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -4226,7 +4226,7 @@
         <v>52169.946891596301</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>43</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>79328.456983629396</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>52522.976241286102</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -4277,7 +4277,7 @@
         <v>64575.052854122601</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>43</v>
       </c>
@@ -4294,7 +4294,7 @@
         <v>79328.456983629396</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>43</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>79328.456983629396</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>43</v>
       </c>
@@ -4328,7 +4328,7 @@
         <v>44361.727511333796</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>90138.015670725901</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -4362,7 +4362,7 @@
         <v>110096.219931271</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -4379,7 +4379,7 @@
         <v>98527.813344714697</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -4396,7 +4396,7 @@
         <v>85972.451790633597</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>50</v>
       </c>
@@ -4413,7 +4413,7 @@
         <v>98527.813344714697</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>50</v>
       </c>
@@ -4430,7 +4430,7 @@
         <v>93484.508001361901</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>50</v>
       </c>
@@ -4447,7 +4447,7 @@
         <v>102147.605083088</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -4464,7 +4464,7 @@
         <v>80645.176868284398</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>59</v>
       </c>
@@ -4481,7 +4481,7 @@
         <v>57122.248458611997</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>59</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>118371.466214944</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>59</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>75183.068783068695</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>59</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>50350.189393939298</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>59</v>
       </c>
@@ -4549,7 +4549,7 @@
         <v>75183.068783068695</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>59</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>63495.951107715802</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>59</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>85639.963545226696</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>59</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>43140.0642368384</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -4617,7 +4617,7 @@
         <v>96346.529814271693</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -4634,7 +4634,7 @@
         <v>96346.529814271693</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>114170.92271024801</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>50</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>96346.529814271693</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>72</v>
       </c>
@@ -4685,7 +4685,7 @@
         <v>50523.144168962303</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>72</v>
       </c>
@@ -4702,7 +4702,7 @@
         <v>50523.144168962303</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>72</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>44814.336744932698</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>72</v>
       </c>
@@ -4736,7 +4736,7 @@
         <v>50522.9917355371</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>72</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>50916.854622170998</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>72</v>
       </c>
@@ -4770,7 +4770,7 @@
         <v>61629.400986610199</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>50</v>
       </c>
@@ -4787,7 +4787,7 @@
         <v>108744.977868573</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>50</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>124053.76344086</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>50</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>108110.94819159299</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -4838,7 +4838,7 @@
         <v>50024.176548089497</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>91</v>
       </c>
@@ -4855,7 +4855,7 @@
         <v>62530.448506807203</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>94</v>
       </c>
@@ -4872,7 +4872,7 @@
         <v>74910.140364685794</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>94</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>77251.082251082204</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>25</v>
       </c>
@@ -4906,7 +4906,7 @@
         <v>66933.828076685197</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>104247.04184704099</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>25</v>
       </c>
@@ -4940,7 +4940,7 @@
         <v>60044.252044252004</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>25</v>
       </c>
@@ -4957,7 +4957,7 @@
         <v>72101.010101010004</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>25</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>86872.534872534801</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>25</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>66933.828076685197</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>25</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>50398.845598845597</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>86</v>
       </c>
@@ -5025,7 +5025,7 @@
         <v>77221.039829735499</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>86</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>77221.039829735499</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>86</v>
       </c>
@@ -5059,7 +5059,7 @@
         <v>77221.039829735499</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>86</v>
       </c>

--- a/data/processed/instances/graphs/voll_table.xlsx
+++ b/data/processed/instances/graphs/voll_table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://auroraer-my.sharepoint.com/personal/farhad_billimoria_auroraer_com/Documents/Documents/Personal/Endog_demand_AI/pyai/data/processed/instances/graphs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FarhadBillimoria\OneDrive - Aurora Energy Research\Documents\Personal\Endog_demand_AI\pyai\data\processed\instances\graphs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{B9D830C9-6F59-4DA8-B47A-6320029FC84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77566856-12F3-41BC-B3CF-A294C2D2F690}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C52436B5-D0F5-4D61-9306-0564EC0AE71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EE0F3C9F-908A-40EA-9D05-B964B7DDA71B}"/>
+    <workbookView xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="15810" xr2:uid="{EE0F3C9F-908A-40EA-9D05-B964B7DDA71B}"/>
   </bookViews>
   <sheets>
     <sheet name="voll_box_panel_by_gpu_ondemand_" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="119">
   <si>
     <t>gpu_model_clean</t>
   </si>
@@ -389,6 +389,12 @@
   </si>
   <si>
     <t>On-demand SLA</t>
+  </si>
+  <si>
+    <t>Inference</t>
+  </si>
+  <si>
+    <t>Training</t>
   </si>
 </sst>
 </file>
@@ -872,7 +878,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -886,6 +892,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1262,15 +1269,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{609544C3-728D-45D7-8E80-16B470978117}">
   <dimension ref="A1:AA77"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.85546875" customWidth="1"/>
-    <col min="14" max="16" width="21.85546875" customWidth="1"/>
-    <col min="21" max="21" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.81640625" customWidth="1"/>
+    <col min="14" max="16" width="21.81640625" customWidth="1"/>
+    <col min="21" max="21" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1299,7 +1306,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>97</v>
       </c>
@@ -1327,8 +1334,11 @@
       <c r="I2">
         <v>85384.3015838188</v>
       </c>
-    </row>
-    <row r="3" spans="1:27" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N2" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -1381,7 +1391,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -1446,7 +1456,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1524,7 +1534,7 @@
         <v>39800</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1602,7 +1612,7 @@
         <v>90900</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1680,7 +1690,7 @@
         <v>108300</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1758,7 +1768,7 @@
         <v>122500</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1788,7 +1798,7 @@
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1816,7 +1826,7 @@
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1853,7 +1863,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1881,8 +1891,11 @@
       <c r="I12">
         <v>18271.140939597299</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="N12" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1910,8 +1923,31 @@
       <c r="I13">
         <v>26756.274400446098</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="M13" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="S13" t="s">
+        <v>104</v>
+      </c>
+      <c r="T13" t="s">
+        <v>105</v>
+      </c>
+      <c r="U13" t="s">
+        <v>116</v>
+      </c>
+      <c r="V13" t="s">
+        <v>104</v>
+      </c>
+      <c r="X13" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1939,8 +1975,44 @@
       <c r="I14">
         <v>26756.274400446098</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="M14" t="s">
+        <v>109</v>
+      </c>
+      <c r="N14" t="s">
+        <v>115</v>
+      </c>
+      <c r="O14" t="s">
+        <v>110</v>
+      </c>
+      <c r="S14" t="s">
+        <v>108</v>
+      </c>
+      <c r="T14" t="s">
+        <v>108</v>
+      </c>
+      <c r="U14" t="s">
+        <v>108</v>
+      </c>
+      <c r="V14" t="s">
+        <v>106</v>
+      </c>
+      <c r="W14" t="s">
+        <v>107</v>
+      </c>
+      <c r="X14" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1968,8 +2040,62 @@
       <c r="I15">
         <v>13408.2373026035</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="L15" t="s">
+        <v>11</v>
+      </c>
+      <c r="M15" s="1" t="str">
+        <f>"$"&amp;V15&amp;" - "&amp;W15&amp;"/MWh"</f>
+        <v>$1800 - 3900/MWh</v>
+      </c>
+      <c r="N15" s="1" t="str">
+        <f>"$"&amp;Z15&amp;" - "&amp;AA15&amp;"/MWh"</f>
+        <v>$15200 - 32600/MWh</v>
+      </c>
+      <c r="O15" s="1" t="str">
+        <f>"$"&amp;X15&amp;" - "&amp;Y15&amp;"/MWh"</f>
+        <v>$600 - 1500/MWh</v>
+      </c>
+      <c r="R15" t="s">
+        <v>11</v>
+      </c>
+      <c r="S15">
+        <f>ROUND(MEDIAN($D$5:$D$18),-2)</f>
+        <v>2600</v>
+      </c>
+      <c r="T15">
+        <f>ROUND(MEDIAN($F$5:$F$18),-2)</f>
+        <v>1000</v>
+      </c>
+      <c r="U15">
+        <f>ROUND(MEDIAN($H$5:$H$18),-2)</f>
+        <v>21500</v>
+      </c>
+      <c r="V15">
+        <f>ROUND(PERCENTILE($D$5:$D$18,0.1),-2)</f>
+        <v>1800</v>
+      </c>
+      <c r="W15">
+        <f>ROUND(PERCENTILE($D$5:$D$18,0.9),-2)</f>
+        <v>3900</v>
+      </c>
+      <c r="X15">
+        <f>ROUND(PERCENTILE($F$5:$F$18,0.1),-2)</f>
+        <v>600</v>
+      </c>
+      <c r="Y15">
+        <f>ROUND(PERCENTILE($F$5:$F$18,0.9),-2)</f>
+        <v>1500</v>
+      </c>
+      <c r="Z15">
+        <f>ROUND(PERCENTILE($H$5:$H$18,0.1),-2)</f>
+        <v>15200</v>
+      </c>
+      <c r="AA15">
+        <f>ROUND(PERCENTILE($H$5:$H$18,0.9),-2)</f>
+        <v>32600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -1991,8 +2117,62 @@
       <c r="I16">
         <v>45424.141076314903</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L16" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" s="1" t="str">
+        <f t="shared" ref="M16:M18" si="1">"$"&amp;V16&amp;" - "&amp;W16&amp;"/MWh"</f>
+        <v>$5900 - 9000/MWh</v>
+      </c>
+      <c r="N16" s="1" t="str">
+        <f>"$"&amp;Z16&amp;" - "&amp;AA16&amp;"/MWh"</f>
+        <v>$49100 - 74300/MWh</v>
+      </c>
+      <c r="O16" s="1" t="str">
+        <f>"$"&amp;X16&amp;" - "&amp;Y16&amp;"/MWh"</f>
+        <v>$1100 - 2600/MWh</v>
+      </c>
+      <c r="R16" t="s">
+        <v>26</v>
+      </c>
+      <c r="S16">
+        <f>ROUND(MEDIAN($D$67:$D$77),-2)</f>
+        <v>7600</v>
+      </c>
+      <c r="T16">
+        <f>ROUND(MEDIAN($F$67:$F$77),-2)</f>
+        <v>2200</v>
+      </c>
+      <c r="U16">
+        <f>ROUND(MEDIAN($H$67:$H$77),-2)</f>
+        <v>63200</v>
+      </c>
+      <c r="V16">
+        <f>ROUND(PERCENTILE($D$67:$D$77,0.1),-2)</f>
+        <v>5900</v>
+      </c>
+      <c r="W16">
+        <f>ROUND(PERCENTILE($D$67:$D$77,0.9),-2)</f>
+        <v>9000</v>
+      </c>
+      <c r="X16">
+        <f>ROUND(PERCENTILE($F$67:$F$77,0.1),-2)</f>
+        <v>1100</v>
+      </c>
+      <c r="Y16">
+        <f>ROUND(PERCENTILE($F$67:$F$77,0.9),-2)</f>
+        <v>2600</v>
+      </c>
+      <c r="Z16">
+        <f>ROUND(PERCENTILE($H$67:$H$77,0.1),-2)</f>
+        <v>49100</v>
+      </c>
+      <c r="AA16">
+        <f>ROUND(PERCENTILE($H$67:$H$77,0.9),-2)</f>
+        <v>74300</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>82</v>
       </c>
@@ -2014,8 +2194,62 @@
       <c r="I17">
         <v>45424.141076314903</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L17" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>$5000 - 10700/MWh</v>
+      </c>
+      <c r="N17" s="1" t="str">
+        <f>"$"&amp;Z17&amp;" - "&amp;AA17&amp;"/MWh"</f>
+        <v>$41300 - 88600/MWh</v>
+      </c>
+      <c r="O17" s="1" t="str">
+        <f>"$"&amp;X17&amp;" - "&amp;Y17&amp;"/MWh"</f>
+        <v>$1700 - 4900/MWh</v>
+      </c>
+      <c r="R17" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17">
+        <f>ROUND(MEDIAN($D$19:$D$66),-2)</f>
+        <v>7600</v>
+      </c>
+      <c r="T17">
+        <f>ROUND(MEDIAN($F$19:$F$66),-2)</f>
+        <v>3100</v>
+      </c>
+      <c r="U17">
+        <f>ROUND(MEDIAN($H$19:$H$66),-2)</f>
+        <v>63500</v>
+      </c>
+      <c r="V17">
+        <f>ROUND(PERCENTILE($D$19:$D$66,0.1),-2)</f>
+        <v>5000</v>
+      </c>
+      <c r="W17">
+        <f>ROUND(PERCENTILE($D$19:$D$66,0.9),-2)</f>
+        <v>10700</v>
+      </c>
+      <c r="X17">
+        <f>ROUND(PERCENTILE($F$19:$F$66,0.1),-2)</f>
+        <v>1700</v>
+      </c>
+      <c r="Y17">
+        <f>ROUND(PERCENTILE($F$19:$F$66,0.9),-2)</f>
+        <v>4900</v>
+      </c>
+      <c r="Z17">
+        <f>ROUND(PERCENTILE($H$19:$H$66,0.1),-2)</f>
+        <v>41300</v>
+      </c>
+      <c r="AA17">
+        <f>ROUND(PERCENTILE($H$19:$H$66,0.9),-2)</f>
+        <v>88600</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>82</v>
       </c>
@@ -2037,8 +2271,62 @@
       <c r="I18">
         <v>23869.62773606</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L18" t="s">
+        <v>98</v>
+      </c>
+      <c r="M18" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>$8900 - 12100/MWh</v>
+      </c>
+      <c r="N18" s="1" t="str">
+        <f>"$"&amp;Z18&amp;" - "&amp;AA18&amp;"/MWh"</f>
+        <v>$73900 - 100200/MWh</v>
+      </c>
+      <c r="O18" s="1" t="str">
+        <f>"$"&amp;X18&amp;" - "&amp;Y18&amp;"/MWh"</f>
+        <v>$2300 - 2800/MWh</v>
+      </c>
+      <c r="R18" t="s">
+        <v>98</v>
+      </c>
+      <c r="S18">
+        <f>ROUND(MEDIAN($D$2:$D$4),-2)</f>
+        <v>10800</v>
+      </c>
+      <c r="T18">
+        <f>ROUND(MEDIAN($F$2:$F$4),-2)</f>
+        <v>2500</v>
+      </c>
+      <c r="U18">
+        <f>ROUND(MEDIAN($H$2:$H$4),-2)</f>
+        <v>89800</v>
+      </c>
+      <c r="V18">
+        <f>ROUND(PERCENTILE($D$2:$D$4,0.1),-2)</f>
+        <v>8900</v>
+      </c>
+      <c r="W18">
+        <f>ROUND(PERCENTILE($D$2:$D$4,0.9),-2)</f>
+        <v>12100</v>
+      </c>
+      <c r="X18">
+        <f>ROUND(PERCENTILE($F$2:$F$4,0.1),-2)</f>
+        <v>2300</v>
+      </c>
+      <c r="Y18">
+        <f>ROUND(PERCENTILE($F$2:$F$4,0.9),-2)</f>
+        <v>2800</v>
+      </c>
+      <c r="Z18">
+        <f>ROUND(PERCENTILE($H$2:$H$4,0.1),-2)</f>
+        <v>73900</v>
+      </c>
+      <c r="AA18">
+        <f>ROUND(PERCENTILE($H$2:$H$4,0.9),-2)</f>
+        <v>100200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -2066,8 +2354,14 @@
       <c r="I19">
         <v>95306.159635571297</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L19" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="2"/>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -2095,8 +2389,12 @@
       <c r="I20">
         <v>64260.988260988197</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="2"/>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -2125,7 +2423,7 @@
         <v>102000.600060005</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -2154,7 +2452,7 @@
         <v>77588.613406795193</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -2183,7 +2481,7 @@
         <v>58622.3776223776</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -2212,7 +2510,7 @@
         <v>77588.613406795193</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -2241,7 +2539,7 @@
         <v>69230.611196712794</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -2270,7 +2568,7 @@
         <v>84343.711083437098</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -2299,7 +2597,7 @@
         <v>52169.946891596301</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>43</v>
       </c>
@@ -2328,7 +2626,7 @@
         <v>79328.456983629396</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -2357,7 +2655,7 @@
         <v>52522.976241286102</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -2386,7 +2684,7 @@
         <v>64575.052854122601</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>43</v>
       </c>
@@ -2415,7 +2713,7 @@
         <v>79328.456983629396</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>43</v>
       </c>
@@ -2444,7 +2742,7 @@
         <v>79328.456983629396</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>43</v>
       </c>
@@ -2473,7 +2771,7 @@
         <v>44361.727511333796</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -2502,7 +2800,7 @@
         <v>90138.015670725901</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -2531,7 +2829,7 @@
         <v>110096.219931271</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -2560,7 +2858,7 @@
         <v>98527.813344714697</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -2589,7 +2887,7 @@
         <v>85972.451790633597</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>50</v>
       </c>
@@ -2618,7 +2916,7 @@
         <v>98527.813344714697</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>50</v>
       </c>
@@ -2647,7 +2945,7 @@
         <v>93484.508001361901</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>50</v>
       </c>
@@ -2676,7 +2974,7 @@
         <v>102147.605083088</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -2705,7 +3003,7 @@
         <v>80645.176868284398</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>59</v>
       </c>
@@ -2734,7 +3032,7 @@
         <v>57122.248458611997</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>59</v>
       </c>
@@ -2763,7 +3061,7 @@
         <v>118371.466214944</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>59</v>
       </c>
@@ -2792,7 +3090,7 @@
         <v>75183.068783068695</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>59</v>
       </c>
@@ -2821,7 +3119,7 @@
         <v>50350.189393939298</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>59</v>
       </c>
@@ -2850,7 +3148,7 @@
         <v>75183.068783068695</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>59</v>
       </c>
@@ -2879,7 +3177,7 @@
         <v>63495.951107715802</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>59</v>
       </c>
@@ -2908,7 +3206,7 @@
         <v>85639.963545226696</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>59</v>
       </c>
@@ -2937,7 +3235,7 @@
         <v>43140.0642368384</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -2966,7 +3264,7 @@
         <v>96346.529814271693</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -2995,7 +3293,7 @@
         <v>96346.529814271693</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -3024,7 +3322,7 @@
         <v>114170.92271024801</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>50</v>
       </c>
@@ -3053,7 +3351,7 @@
         <v>96346.529814271693</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>72</v>
       </c>
@@ -3082,7 +3380,7 @@
         <v>50523.144168962303</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>72</v>
       </c>
@@ -3111,7 +3409,7 @@
         <v>50523.144168962303</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>72</v>
       </c>
@@ -3140,7 +3438,7 @@
         <v>44814.336744932698</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>72</v>
       </c>
@@ -3169,7 +3467,7 @@
         <v>50522.9917355371</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>72</v>
       </c>
@@ -3198,7 +3496,7 @@
         <v>50916.854622170998</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>72</v>
       </c>
@@ -3227,7 +3525,7 @@
         <v>61629.400986610199</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>50</v>
       </c>
@@ -3256,7 +3554,7 @@
         <v>108744.977868573</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>50</v>
       </c>
@@ -3285,7 +3583,7 @@
         <v>124053.76344086</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>50</v>
       </c>
@@ -3314,7 +3612,7 @@
         <v>108110.94819159299</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -3343,7 +3641,7 @@
         <v>50024.176548089497</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>91</v>
       </c>
@@ -3372,7 +3670,7 @@
         <v>62530.448506807203</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>94</v>
       </c>
@@ -3401,7 +3699,7 @@
         <v>74910.140364685794</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>94</v>
       </c>
@@ -3430,7 +3728,7 @@
         <v>77251.082251082204</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>25</v>
       </c>
@@ -3459,7 +3757,7 @@
         <v>66933.828076685197</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -3488,7 +3786,7 @@
         <v>104247.04184704099</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>25</v>
       </c>
@@ -3517,7 +3815,7 @@
         <v>60044.252044252004</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>25</v>
       </c>
@@ -3546,7 +3844,7 @@
         <v>72101.010101010004</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>25</v>
       </c>
@@ -3575,7 +3873,7 @@
         <v>86872.534872534801</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>25</v>
       </c>
@@ -3604,7 +3902,7 @@
         <v>66933.828076685197</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>25</v>
       </c>
@@ -3633,7 +3931,7 @@
         <v>50398.845598845597</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>86</v>
       </c>
@@ -3662,7 +3960,7 @@
         <v>77221.039829735499</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>86</v>
       </c>
@@ -3691,7 +3989,7 @@
         <v>77221.039829735499</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>86</v>
       </c>
@@ -3720,7 +4018,7 @@
         <v>77221.039829735499</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -3751,9 +4049,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I1" xr:uid="{609544C3-728D-45D7-8E80-16B470978117}"/>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="L9:N10"/>
     <mergeCell ref="M3:O3"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="L19:N20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -3765,9 +4065,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53B82B0B-DBB3-4D30-BC4C-DDE53B559AE4}">
   <dimension ref="A1:E77"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3784,7 +4084,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>97</v>
       </c>
@@ -3801,7 +4101,7 @@
         <v>85384.3015838188</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -3818,7 +4118,7 @@
         <v>109792.434691745</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -3835,7 +4135,7 @@
         <v>125683.444976076</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -3852,7 +4152,7 @@
         <v>19290.2476088316</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3869,7 +4169,7 @@
         <v>19290.2476088316</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -3886,7 +4186,7 @@
         <v>26225.055432372501</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -3903,7 +4203,7 @@
         <v>26225.055432372501</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -3920,7 +4220,7 @@
         <v>26225.055432372501</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -3937,7 +4237,7 @@
         <v>19891.356446716702</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -3954,7 +4254,7 @@
         <v>26756.274400446098</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -3971,7 +4271,7 @@
         <v>18271.140939597299</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -3988,7 +4288,7 @@
         <v>26756.274400446098</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -4005,7 +4305,7 @@
         <v>26756.274400446098</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -4022,7 +4322,7 @@
         <v>13408.2373026035</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -4039,7 +4339,7 @@
         <v>45424.141076314903</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>82</v>
       </c>
@@ -4056,7 +4356,7 @@
         <v>45424.141076314903</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>82</v>
       </c>
@@ -4073,7 +4373,7 @@
         <v>23869.62773606</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -4090,7 +4390,7 @@
         <v>95306.159635571297</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -4107,7 +4407,7 @@
         <v>64260.988260988197</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -4124,7 +4424,7 @@
         <v>102000.600060005</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -4141,7 +4441,7 @@
         <v>77588.613406795193</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -4158,7 +4458,7 @@
         <v>58622.3776223776</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -4175,7 +4475,7 @@
         <v>77588.613406795193</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -4192,7 +4492,7 @@
         <v>69230.611196712794</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -4209,7 +4509,7 @@
         <v>84343.711083437098</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -4226,7 +4526,7 @@
         <v>52169.946891596301</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>43</v>
       </c>
@@ -4243,7 +4543,7 @@
         <v>79328.456983629396</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -4260,7 +4560,7 @@
         <v>52522.976241286102</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>43</v>
       </c>
@@ -4277,7 +4577,7 @@
         <v>64575.052854122601</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>43</v>
       </c>
@@ -4294,7 +4594,7 @@
         <v>79328.456983629396</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>43</v>
       </c>
@@ -4311,7 +4611,7 @@
         <v>79328.456983629396</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>43</v>
       </c>
@@ -4328,7 +4628,7 @@
         <v>44361.727511333796</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -4345,7 +4645,7 @@
         <v>90138.015670725901</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>50</v>
       </c>
@@ -4362,7 +4662,7 @@
         <v>110096.219931271</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -4379,7 +4679,7 @@
         <v>98527.813344714697</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>50</v>
       </c>
@@ -4396,7 +4696,7 @@
         <v>85972.451790633597</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>50</v>
       </c>
@@ -4413,7 +4713,7 @@
         <v>98527.813344714697</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>50</v>
       </c>
@@ -4430,7 +4730,7 @@
         <v>93484.508001361901</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>50</v>
       </c>
@@ -4447,7 +4747,7 @@
         <v>102147.605083088</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>50</v>
       </c>
@@ -4464,7 +4764,7 @@
         <v>80645.176868284398</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>59</v>
       </c>
@@ -4481,7 +4781,7 @@
         <v>57122.248458611997</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>59</v>
       </c>
@@ -4498,7 +4798,7 @@
         <v>118371.466214944</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>59</v>
       </c>
@@ -4515,7 +4815,7 @@
         <v>75183.068783068695</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>59</v>
       </c>
@@ -4532,7 +4832,7 @@
         <v>50350.189393939298</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>59</v>
       </c>
@@ -4549,7 +4849,7 @@
         <v>75183.068783068695</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>59</v>
       </c>
@@ -4566,7 +4866,7 @@
         <v>63495.951107715802</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>59</v>
       </c>
@@ -4583,7 +4883,7 @@
         <v>85639.963545226696</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>59</v>
       </c>
@@ -4600,7 +4900,7 @@
         <v>43140.0642368384</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -4617,7 +4917,7 @@
         <v>96346.529814271693</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -4634,7 +4934,7 @@
         <v>96346.529814271693</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -4651,7 +4951,7 @@
         <v>114170.92271024801</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>50</v>
       </c>
@@ -4668,7 +4968,7 @@
         <v>96346.529814271693</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>72</v>
       </c>
@@ -4685,7 +4985,7 @@
         <v>50523.144168962303</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>72</v>
       </c>
@@ -4702,7 +5002,7 @@
         <v>50523.144168962303</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>72</v>
       </c>
@@ -4719,7 +5019,7 @@
         <v>44814.336744932698</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>72</v>
       </c>
@@ -4736,7 +5036,7 @@
         <v>50522.9917355371</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>72</v>
       </c>
@@ -4753,7 +5053,7 @@
         <v>50916.854622170998</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>72</v>
       </c>
@@ -4770,7 +5070,7 @@
         <v>61629.400986610199</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>50</v>
       </c>
@@ -4787,7 +5087,7 @@
         <v>108744.977868573</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>50</v>
       </c>
@@ -4804,7 +5104,7 @@
         <v>124053.76344086</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>50</v>
       </c>
@@ -4821,7 +5121,7 @@
         <v>108110.94819159299</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -4838,7 +5138,7 @@
         <v>50024.176548089497</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>91</v>
       </c>
@@ -4855,7 +5155,7 @@
         <v>62530.448506807203</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>94</v>
       </c>
@@ -4872,7 +5172,7 @@
         <v>74910.140364685794</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>94</v>
       </c>
@@ -4889,7 +5189,7 @@
         <v>77251.082251082204</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>25</v>
       </c>
@@ -4906,7 +5206,7 @@
         <v>66933.828076685197</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -4923,7 +5223,7 @@
         <v>104247.04184704099</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>25</v>
       </c>
@@ -4940,7 +5240,7 @@
         <v>60044.252044252004</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>25</v>
       </c>
@@ -4957,7 +5257,7 @@
         <v>72101.010101010004</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>25</v>
       </c>
@@ -4974,7 +5274,7 @@
         <v>86872.534872534801</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>25</v>
       </c>
@@ -4991,7 +5291,7 @@
         <v>66933.828076685197</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>25</v>
       </c>
@@ -5008,7 +5308,7 @@
         <v>50398.845598845597</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>86</v>
       </c>
@@ -5025,7 +5325,7 @@
         <v>77221.039829735499</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>86</v>
       </c>
@@ -5042,7 +5342,7 @@
         <v>77221.039829735499</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>86</v>
       </c>
@@ -5059,7 +5359,7 @@
         <v>77221.039829735499</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>86</v>
       </c>
